--- a/data/daily/2026-09/2026-09-30.xlsx
+++ b/data/daily/2026-09/2026-09-30.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1425,102 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,24 +1528,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1553,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,154 +1578,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,22 +2596,22 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16162</v>
+        <v>16165</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용 패키지 만족 — 예쁜 패키징과 실용적인 구성으로 선물받을 때 기분이 좋음</t>
+          <t>간편한 섭취 및 휴대 — 액상과 정제가 함께 구성되어 언제 어디서나 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>간편한 섭취 방법 — 복용이 간편하여 일상에서 건강을 챙기기 적합함</t>
+          <t>선물용 고급 포장 — 패키지 디자인이 예쁘고 실용적이어서 선물받았을 때 만족도가 높음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>체감 효과 미미 — 가끔 섭취할 경우 눈에 띄는 효과를 느끼기 어려움</t>
+          <t>즉각적 효과 미흡 — 단기간이나 가끔 섭취할 경우 눈에 띄는 효과를 바로 느끼기 어려움</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2655,20 +2655,24 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15497</v>
+        <v>15500</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>편리한 섭취와 좋은 맛 — 정제 2알과 액상이 함께 있어 편리하며 맛이 자극적이지 않고 맛있음</t>
+          <t>물 없는 간편 섭취 — 물 없이 들고 다니며 간편하게 먹을 수 있어 휴대성이 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>선물 구성 및 패키지 — 박스 포장이 깔끔하며 증정 구성이 들어있어 선물용으로 적합함</t>
+          <t>피로 회복 및 활력 — 컨디션이 안 좋거나 피곤할 때 섭취하면 활력을 얻는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>공복 섭취 시 메스꺼움 — 빈속에 복용할 경우 속이 울렁거리고 토할 것 같은 불편함이 발생할 수 있음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2714,18 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>섭취 편의와 피로 개선 — 먹기 편하고 피로 회복 및 활력 충전에 도움이 됨</t>
+          <t>활력 충전 효과 — 섭취 후 에너지와 힘이 나며 컨디션 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>빠른 배송과 선물 만족도 — 배송이 빠르고 명절이나 위로 선물용으로 만족도가 높음</t>
+          <t>부담 없는 선물용 — 신뢰도 높은 브랜드 제품으로 명절이나 위로 선물로 전하기에 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>완충재 부족 및 박스 훼손 — 배송 시 완충재가 없어 박스가 찌그러져 도착함</t>
+          <t>배송 완충재 부족 — 포장 시 완충재가 들어있지 않아 제품 박스가 찌그러져서 배송됨</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2769,22 +2773,22 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체력 보충 및 피로 회복 — 피곤할 때나 힘을 내야 할 때 섭취 시 에너지 보충에 도움이 됨</t>
+          <t>체력 방전 예방 — 피로도가 높거나 육아·일상에서 지칠 때 체력을 유지하는 데 도움이 됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>개별 포장의 편리함 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 좋음</t>
+          <t>편리한 개별 포장 — 한 포씩 개별 포장되어 있어 가방이나 책상에 두고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 사전 요청이 반영되지 않고 문 앞에 배송됨</t>
+          <t>배송 요청사항 미반영 — 오피스텔 관리실 위탁 등 사전 요청한 배송 메시지가 지켜지지 않고 문 앞에 배송됨</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2832,12 +2836,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 마이구미처럼 맛있는 젤리 형태라 영양제 느낌 없이 맛있게 먹기 좋음</t>
+          <t>맛있는 젤리 형태 — 마이구미처럼 달콤하고 맛있는 젤리 제형이라 거부감 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>물 없이 간편한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 간편하게 섭취할 수 있음</t>
+          <t>물 없이 편한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 간편하게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2848,7 +2852,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2856,58 +2860,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>1703</v>
+        <v>8732</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>상큼한 맛과 목넘김 — 맛이 상큼하고 부드러워 목넘김이 좋음</t>
+          <t>듀얼 제형의 편의성 — 액상과 정제가 함께 들어있어 물 없이도 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 방식 — 뚜껑을 눌러 섞어 마시는 신선함과 고급스러운 포장이 만족스러움</t>
+          <t>피로 회복 효과 — 기력이 떨어지거나 피곤할 때 활력을 더해주는 데 효과적임</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>분말 침전 현상 — 가루가 용기 밑에 가라앉아 반드시 잘 흔들어 마셔야 함</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2915,54 +2915,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8732</v>
+        <v>1704</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>물 없이 간편한 듀얼 제형 — 액상과 정제가 함께 있어 물 없이 어디서나 간편히 섭취 가능함</t>
+          <t>상큼한 맛과 목넘김 — 맛이 상큼하고 부드러워 목넘김이 좋고 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 기력이 떨어지거나 힘이 없을 때 섭취하면 활력이 생김</t>
+          <t>색다른 복용 방식 — 뚜껑을 눌러 발포 성분을 섞어 마시는 신기하고 재미있는 제형임</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>가루 침전물 발생 — 분말이 밑에 가라앉을 수 있어 복용 전 충분히 흔들어 마셔야 함</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2970,49 +2974,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11090567</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928083206_e0dd807ea02f482d93440e2a32dfd08d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>215</v>
+        <v>776</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>피로 개선 및 알찬 구성 — 고함량이라 피로 회복에 효과적이며 30일분 구성으로 알참</t>
+          <t>성별 맞춤형 구성 — 남성과 여성용으로 분리되어 있어 상황에 맞게 옵션 선택이 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>정성스러운 선물 포장 — 패키지가 정성스러워 생일이나 명절 선물용으로 기분 좋게 주고받음</t>
+          <t>쓰지 않은 편안한 맛 — 비타민 특유의 쓴맛이 없어 복용하기 편하고 피로 개선에 도움을 줌</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>제품 오염 및 봉인 훼손 — 쇼핑백과 상자에 먼지가 묻어있거나 밀봉 스티커가 떨어져 있음</t>
+          <t>큰 알약 크기 — 정제의 크기가 다소 커서 한 번에 삼키기 힘들 수 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3021,7 +3025,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3029,49 +3033,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928083206_e0dd807ea02f482d93440e2a32dfd08d.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>776</v>
+        <v>215</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성용과 여성용이 구분되어 맞춤형 영양 보충이 가능함</t>
+          <t>피로 개선 도움 — 하루 하나씩 챙겨 먹으면 피로감이 줄어들고 컨디션 유지에 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>쓴맛 없는 간편한 섭취 — 비타민 특유의 쓴맛이 없고 휴대하며 챙겨 먹기 편함</t>
+          <t>정성스러운 선물 패키지 — 선물 세트 구성과 패키징이 정성스러워 생일 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>상품 포장 위생 상태 — 상자 및 쇼핑백에 먼지가 묻어있거나 밀봉 스티커가 떼어지고 지문이 묻어 배송됨</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3115,16 +3119,16 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 액상이 함유되어 흡수가 빠른 느낌이며 피로 회복 및 컨디션 유지에 좋음</t>
+          <t>빠른 체내 흡수 — 액상 제형이 함께 들어있어 체내 흡수가 빠르고 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 외출 시 한 병씩 챙겨 나갈 수 있어 섭취가 매우 편리함</t>
+          <t>외출 시 뛰어난 휴대성 — 외출할 때 스틱이나 병 하나만 챙겨 나가면 되어 복용이 편리함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -3174,18 +3178,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 포장이 고급스럽고 예뻐서 선물받았을 때 기분이 좋아짐</t>
+          <t>고급스러운 포장 — 오간자 패키징 포장이 예쁘고 고급스러워 선물용으로 감동을 줌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>간편한 앰플 제형 — 낱개 앰플 형태라 하나씩 따서 마시기 편하고 맛도 양호함</t>
+          <t>간편한 앰플 섭취 — 낱개로 포장된 앰플 형태라 하나씩 따서 마시기 편함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 가격대가 다소 높은 편이라 할인할 때 구매를 고려하게 됨</t>
+          <t>비싼 가격대 — 제품의 가격대가 다소 비싼 편이라 할인 시기에 구매를 노리게 됨</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3233,12 +3237,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>구수한 고구마 맛 — 고구마 맛이 나 구수하고 거부감 없이 맛있게 먹기 좋음</t>
+          <t>구수한 고구마 맛 — 고소하고 구수한 고구마 맛이 나 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편안함 — 식후 섭취 시 더부룩함이 줄어들고 소화 및 속 편안함에 도움을 줌</t>
+          <t>소화 및 속 편안함 — 식후 복용 시 속이 편안해지고 소화와 배변 활동에 도움을 줌</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -3288,23 +3292,23 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>맛과 포만감 — 닭가슴살 맛이 우수하고 식감이 좋아 하나만 먹어도 포만감이 큼</t>
+          <t>높은 포만감과 맛 — 하나만 먹어도 포만감이 오래 가며 카레 등 맛이 다양하고 뛰어남</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>다양한 식단 구성 — 다양한 맛과 종류로 구성되어 있어 질리지 않고 식단 관리하기 좋음</t>
+          <t>다채로운 상품 구성 — 한 달 식단용으로 여러 가지 맛을 종류별로 맛볼 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>오배송 및 구성 누락 — 주문한 구성품이 누락되거나 중복 배송되는 오배송 발생함</t>
+          <t>제품 배송 오입고 — 주문한 수량과 다르게 일부 상품이 누락되거나 중복하여 잘못 도착함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>포장 터짐 및 진공 불량 — 제품이 터져 소스가 새어 나오거나 진공 포장이 헐렁함</t>
+          <t>포장 파손 및 소스 누출 — 비닐 포장이 헐렁하여 제품이 터지고 소스가 묻은 상태로 배송됨</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -3351,12 +3355,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>부드럽고 냄새 없는 맛 — 닭가슴살 특유의 냄새가 나지 않고 부드러워 맛있게 먹을 수 있음</t>
+          <t>잡내 없는 부드러움 — 닭가슴살 특유의 냄새가 나지 않고 식감이 매우 부드러움</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다양한 종류와 가성비 — 소스 닭가슴살부터 주먹밥까지 구성이 다양하여 가성비가 훌륭함</t>
+          <t>다양하고 질리지 않는 맛 — 소스, 스테이크 등 종류가 풍부하여 질리지 않고 다이어트 식단 유지가 가능함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -3375,51 +3379,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>맛있는 베리말차 맛 — 상큼하고 고소한 베리말차 맛으로 씹히는 식감이 있어 맛있음</t>
+          <t>확실한 숙취 완화 — 음주 전후에 복용 시 다음 날 숙취와 몸의 무거움이 줄어듦</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>소화 개선 효과 — 식후 섭취 시 속이 편해지고 소화 더부룩함이 개선됨</t>
+          <t>휴대성 높은 개별 포장 — 작은 스틱 형태의 액상이라 가방이나 주머니에 넣어 다니다 물 없이 먹기 편함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>느린 배송 속도 — 배송이 빠른 편이 아니어서 도착까지 다소 시간이 소요됨</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3434,49 +3434,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 패키지와 전용 쇼핑백이 깔끔하고 고급스러워 선물용으로 적합함</t>
+          <t>속 편한 소화 도움 — 식단 조절이나 식사 후 섭취 시 더부룩함이 사라지고 속이 편안해짐</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>간편한 휴대와 섭취 — 스틱 제형이라 물 없이 언제 어디서나 바로 먹을 수 있음</t>
+          <t>맛있는 베리말차 맛 — 고소하고 상큼한 맛이 나서 질리지 않고 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>한약/쌍화탕 맛 호불호 — 진한 한약재나 쌍화탕 맛이 나서 인분 따라 호불호가 갈릴 수 있음</t>
+          <t>다소 느린 배송 — 다른 판매처 대비 배송 완료까지 시간이 약간 느린 편임</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3493,58 +3493,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965673</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>759</v>
+        <v>215</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 케이스 — 포장과 병 케이스가 매우 예쁘고 고급스러움</t>
+          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비리거나 텁텁한 맛이 없고 초코우유처럼 맛있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 앰플 — 새콤달콤한 비타민 맛이라 섭취에 부담이 없음</t>
+          <t>부드러운 목넘김 — 목넘김이 깔끔하고 인위적인 단맛이 강하지 않아 운동 후 부담 없이 마시기 좋음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>감기약 느낌의 향미 — 비타500과 감기약이 섞인 듯한 맛이 느껴짐</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3552,43 +3548,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091204_17479341408f44afb805d97625daff01.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>215</v>
+        <v>759</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없이 깔끔함</t>
+          <t>예쁜 선물 포장 — 케이스와 포장이 공주님 느낌으로 예쁘고 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>부드러운 목넘김과 맛 — 초코우유나 모카라떼처럼 진하고 맛있으며 목넘김이 부드러움</t>
+          <t>맛있는 앰플 제형 — 새콤달콤한 맛이 나며 약을 잘 못 먹는 사람도 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -3638,12 +3634,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>초고함량으로 활력 보충 — 6,200mg의 고함량이라 운동 전후 및 피로 시 활력 충전에 효과적임</t>
+          <t>초고함량 활력 충전 — 6,200mg 고함량 아르기닌으로 운동 전이나 피로 시 에너지를 높여줌</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 휴대와 섭취 — 스틱 개별 포장이라 챙겨 다니며 하루 한 포씩 간편히 먹기 좋음</t>
+          <t>간편한 1포 섭취 — 하루 한 포 개별 포장되어 있어 가지고 다니며 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -3654,7 +3650,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3662,51 +3658,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13586002</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>1534</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상큼하고 풍부한 과일 생강 맛 — 생강에 과일이 더해져 톡 쏘면서도 상큼하게 마시기 좋음</t>
+          <t>알찬 영양제 세트 — 활력을 주는 아르기닌과 간 건강용 밀크씨슬을 동시에 챙길 수 있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>귀여운 용기와 에너지 충전 — 미니보틀이 귀엽고 아침 공복 섭취 시 기분 전환과 활력 충전에 도움 됨</t>
+          <t>피로 개선 효과 — 아침에 일어날 때 몸이 가벼워지고 운동 시 지치지 않는 데 도움을 줌</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>강한 생강 향미 호불호 — 생강 특유의 알싸하고 매운맛으로 인해 사람에 따라 거부감이 있을 수 있음</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3846,22 +3838,22 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>홍삼/인삼</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3903,22 +3895,22 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>뉴트리포유</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>정관장</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리포유</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>옵티젠</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3960,22 +3952,22 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4028,34 +4020,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16162</v>
+        <v>16165</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15497</v>
+        <v>15500</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3377</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>6489</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1703</v>
+        <v>8732</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8732</v>
+        <v>1704</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>776</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>776</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -4066,62 +4058,62 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용 패키지 만족 — 예쁜 패키징과 실용적인 구성으로 선물받을 때 기분이 좋음
-간편한 섭취 방법 — 복용이 간편하여 일상에서 건강을 챙기기 적합함</t>
+          <t>간편한 섭취 및 휴대 — 액상과 정제가 함께 구성되어 언제 어디서나 간편하게 섭취 가능함
+선물용 고급 포장 — 패키지 디자인이 예쁘고 실용적이어서 선물받았을 때 만족도가 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>편리한 섭취와 좋은 맛 — 정제 2알과 액상이 함께 있어 편리하며 맛이 자극적이지 않고 맛있음
-선물 구성 및 패키지 — 박스 포장이 깔끔하며 증정 구성이 들어있어 선물용으로 적합함</t>
+          <t>물 없는 간편 섭취 — 물 없이 들고 다니며 간편하게 먹을 수 있어 휴대성이 좋음
+피로 회복 및 활력 — 컨디션이 안 좋거나 피곤할 때 섭취하면 활력을 얻는 데 도움이 됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>섭취 편의와 피로 개선 — 먹기 편하고 피로 회복 및 활력 충전에 도움이 됨
-빠른 배송과 선물 만족도 — 배송이 빠르고 명절이나 위로 선물용으로 만족도가 높음</t>
+          <t>활력 충전 효과 — 섭취 후 에너지와 힘이 나며 컨디션 관리에 도움이 됨
+부담 없는 선물용 — 신뢰도 높은 브랜드 제품으로 명절이나 위로 선물로 전하기에 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체력 보충 및 피로 회복 — 피곤할 때나 힘을 내야 할 때 섭취 시 에너지 보충에 도움이 됨
-개별 포장의 편리함 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙겨 먹기 좋음</t>
+          <t>체력 방전 예방 — 피로도가 높거나 육아·일상에서 지칠 때 체력을 유지하는 데 도움이 됨
+편리한 개별 포장 — 한 포씩 개별 포장되어 있어 가방이나 책상에 두고 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 마이구미처럼 맛있는 젤리 형태라 영양제 느낌 없이 맛있게 먹기 좋음
-물 없이 간편한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 간편하게 섭취할 수 있음</t>
+          <t>맛있는 젤리 형태 — 마이구미처럼 달콤하고 맛있는 젤리 제형이라 거부감 없이 먹기 좋음
+물 없이 편한 섭취 — 알약을 잘 못 먹는 사람도 물 없이 간편하게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 맛과 목넘김 — 맛이 상큼하고 부드러워 목넘김이 좋음
-고급스러운 포장과 방식 — 뚜껑을 눌러 섞어 마시는 신선함과 고급스러운 포장이 만족스러움</t>
+          <t>듀얼 제형의 편의성 — 액상과 정제가 함께 들어있어 물 없이도 간편하게 복용 가능함
+피로 회복 효과 — 기력이 떨어지거나 피곤할 때 활력을 더해주는 데 효과적임</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 간편한 듀얼 제형 — 액상과 정제가 함께 있어 물 없이 어디서나 간편히 섭취 가능함
-피로 회복 및 활력 증진 — 기력이 떨어지거나 힘이 없을 때 섭취하면 활력이 생김</t>
+          <t>상큼한 맛과 목넘김 — 맛이 상큼하고 부드러워 목넘김이 좋고 부담 없이 먹을 수 있음
+색다른 복용 방식 — 뚜껑을 눌러 발포 성분을 섞어 마시는 신기하고 재미있는 제형임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 및 알찬 구성 — 고함량이라 피로 회복에 효과적이며 30일분 구성으로 알참
-정성스러운 선물 포장 — 패키지가 정성스러워 생일이나 명절 선물용으로 기분 좋게 주고받음</t>
+          <t>성별 맞춤형 구성 — 남성과 여성용으로 분리되어 있어 상황에 맞게 옵션 선택이 가능함
+쓰지 않은 편안한 맛 — 비타민 특유의 쓴맛이 없어 복용하기 편하고 피로 개선에 도움을 줌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성용과 여성용이 구분되어 맞춤형 영양 보충이 가능함
-쓴맛 없는 간편한 섭취 — 비타민 특유의 쓴맛이 없고 휴대하며 챙겨 먹기 편함</t>
+          <t>피로 개선 도움 — 하루 하나씩 챙겨 먹으면 피로감이 줄어들고 컨디션 유지에 좋음
+정성스러운 선물 패키지 — 선물 세트 구성과 패키징이 정성스러워 생일 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 액상이 함유되어 흡수가 빠른 느낌이며 피로 회복 및 컨디션 유지에 좋음
-우수한 휴대성 — 외출 시 한 병씩 챙겨 나갈 수 있어 섭취가 매우 편리함</t>
+          <t>빠른 체내 흡수 — 액상 제형이 함께 들어있어 체내 흡수가 빠르고 피로 회복에 효과적임
+외출 시 뛰어난 휴대성 — 외출할 때 스틱이나 병 하나만 챙겨 나가면 되어 복용이 편리함</t>
         </is>
       </c>
     </row>
@@ -4133,35 +4125,39 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과 미미 — 가끔 섭취할 경우 눈에 띄는 효과를 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>즉각적 효과 미흡 — 단기간이나 가끔 섭취할 경우 눈에 띄는 효과를 바로 느끼기 어려움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>공복 섭취 시 메스꺼움 — 빈속에 복용할 경우 속이 울렁거리고 토할 것 같은 불편함이 발생할 수 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>완충재 부족 및 박스 훼손 — 배송 시 완충재가 없어 박스가 찌그러져 도착함</t>
+          <t>배송 완충재 부족 — 포장 시 완충재가 들어있지 않아 제품 박스가 찌그러져서 배송됨</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 사전 요청이 반영되지 않고 문 앞에 배송됨</t>
+          <t>배송 요청사항 미반영 — 오피스텔 관리실 위탁 등 사전 요청한 배송 메시지가 지켜지지 않고 문 앞에 배송됨</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>분말 침전 현상 — 가루가 용기 밑에 가라앉아 반드시 잘 흔들어 마셔야 함</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>가루 침전물 발생 — 분말이 밑에 가라앉을 수 있어 복용 전 충분히 흔들어 마셔야 함</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>제품 오염 및 봉인 훼손 — 쇼핑백과 상자에 먼지가 묻어있거나 밀봉 스티커가 떨어져 있음</t>
+          <t>큰 알약 크기 — 정제의 크기가 다소 커서 한 번에 삼키기 힘들 수 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>상품 포장 위생 상태 — 상자 및 쇼핑백에 먼지가 묻어있거나 밀봉 스티커가 떼어지고 지문이 묻어 배송됨</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4199,22 +4195,22 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>39,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>59,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4392,22 +4388,22 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4439,24 +4435,24 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
@@ -4464,7 +4460,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>타이거모닝</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4496,24 +4492,24 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 (고급 오간자 패키징 + 선물용 쇼핑백)</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
-        </is>
-      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
@@ -4521,7 +4517,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -4581,22 +4577,22 @@
         <v>59</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="I19" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>759</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>215</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>11</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -4607,62 +4603,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 포장이 고급스럽고 예뻐서 선물받았을 때 기분이 좋아짐
-간편한 앰플 제형 — 낱개 앰플 형태라 하나씩 따서 마시기 편하고 맛도 양호함</t>
+          <t>고급스러운 포장 — 오간자 패키징 포장이 예쁘고 고급스러워 선물용으로 감동을 줌
+간편한 앰플 섭취 — 낱개로 포장된 앰플 형태라 하나씩 따서 마시기 편함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>구수한 고구마 맛 — 고구마 맛이 나 구수하고 거부감 없이 맛있게 먹기 좋음
-소화 촉진 및 속 편안함 — 식후 섭취 시 더부룩함이 줄어들고 소화 및 속 편안함에 도움을 줌</t>
+          <t>구수한 고구마 맛 — 고소하고 구수한 고구마 맛이 나 거부감 없이 맛있게 먹기 좋음
+소화 및 속 편안함 — 식후 복용 시 속이 편안해지고 소화와 배변 활동에 도움을 줌</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>맛과 포만감 — 닭가슴살 맛이 우수하고 식감이 좋아 하나만 먹어도 포만감이 큼
-다양한 식단 구성 — 다양한 맛과 종류로 구성되어 있어 질리지 않고 식단 관리하기 좋음</t>
+          <t>높은 포만감과 맛 — 하나만 먹어도 포만감이 오래 가며 카레 등 맛이 다양하고 뛰어남
+다채로운 상품 구성 — 한 달 식단용으로 여러 가지 맛을 종류별로 맛볼 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 냄새 없는 맛 — 닭가슴살 특유의 냄새가 나지 않고 부드러워 맛있게 먹을 수 있음
-다양한 종류와 가성비 — 소스 닭가슴살부터 주먹밥까지 구성이 다양하여 가성비가 훌륭함</t>
+          <t>잡내 없는 부드러움 — 닭가슴살 특유의 냄새가 나지 않고 식감이 매우 부드러움
+다양하고 질리지 않는 맛 — 소스, 스테이크 등 종류가 풍부하여 질리지 않고 다이어트 식단 유지가 가능함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 베리말차 맛 — 상큼하고 고소한 베리말차 맛으로 씹히는 식감이 있어 맛있음
-소화 개선 효과 — 식후 섭취 시 속이 편해지고 소화 더부룩함이 개선됨</t>
+          <t>확실한 숙취 완화 — 음주 전후에 복용 시 다음 날 숙취와 몸의 무거움이 줄어듦
+휴대성 높은 개별 포장 — 작은 스틱 형태의 액상이라 가방이나 주머니에 넣어 다니다 물 없이 먹기 편함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 패키지와 전용 쇼핑백이 깔끔하고 고급스러워 선물용으로 적합함
-간편한 휴대와 섭취 — 스틱 제형이라 물 없이 언제 어디서나 바로 먹을 수 있음</t>
+          <t>속 편한 소화 도움 — 식단 조절이나 식사 후 섭취 시 더부룩함이 사라지고 속이 편안해짐
+맛있는 베리말차 맛 — 고소하고 상큼한 맛이 나서 질리지 않고 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 케이스 — 포장과 병 케이스가 매우 예쁘고 고급스러움
-상큼하고 맛있는 앰플 — 새콤달콤한 비타민 맛이라 섭취에 부담이 없음</t>
+          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비리거나 텁텁한 맛이 없고 초코우유처럼 맛있음
+부드러운 목넘김 — 목넘김이 깔끔하고 인위적인 단맛이 강하지 않아 운동 후 부담 없이 마시기 좋음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함과 비린 맛이 없이 깔끔함
-부드러운 목넘김과 맛 — 초코우유나 모카라떼처럼 진하고 맛있으며 목넘김이 부드러움</t>
+          <t>예쁜 선물 포장 — 케이스와 포장이 공주님 느낌으로 예쁘고 고급스러워 선물용으로 적합함
+맛있는 앰플 제형 — 새콤달콤한 맛이 나며 약을 잘 못 먹는 사람도 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>초고함량으로 활력 보충 — 6,200mg의 고함량이라 운동 전후 및 피로 시 활력 충전에 효과적임
-간편한 휴대와 섭취 — 스틱 개별 포장이라 챙겨 다니며 하루 한 포씩 간편히 먹기 좋음</t>
+          <t>초고함량 활력 충전 — 6,200mg 고함량 아르기닌으로 운동 전이나 피로 시 에너지를 높여줌
+간편한 1포 섭취 — 하루 한 포 개별 포장되어 있어 가지고 다니며 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 풍부한 과일 생강 맛 — 생강에 과일이 더해져 톡 쏘면서도 상큼하게 마시기 좋음
-귀여운 용기와 에너지 충전 — 미니보틀이 귀엽고 아침 공복 섭취 시 기분 전환과 활력 충전에 도움 됨</t>
+          <t>알찬 영양제 세트 — 활력을 주는 아르기닌과 간 건강용 밀크씨슬을 동시에 챙길 수 있음
+피로 개선 효과 — 아침에 일어날 때 몸이 가벼워지고 운동 시 지치지 않는 데 도움을 줌</t>
         </is>
       </c>
     </row>
@@ -4674,39 +4670,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 가격대가 다소 높은 편이라 할인할 때 구매를 고려하게 됨</t>
+          <t>비싼 가격대 — 제품의 가격대가 다소 비싼 편이라 할인 시기에 구매를 노리게 됨</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>오배송 및 구성 누락 — 주문한 구성품이 누락되거나 중복 배송되는 오배송 발생함
-포장 터짐 및 진공 불량 — 제품이 터져 소스가 새어 나오거나 진공 포장이 헐렁함</t>
+          <t>제품 배송 오입고 — 주문한 수량과 다르게 일부 상품이 누락되거나 중복하여 잘못 도착함
+포장 파손 및 소스 누출 — 비닐 포장이 헐렁하여 제품이 터지고 소스가 묻은 상태로 배송됨</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>느린 배송 속도 — 배송이 빠른 편이 아니어서 도착까지 다소 시간이 소요됨</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>한약/쌍화탕 맛 호불호 — 진한 한약재나 쌍화탕 맛이 나서 인분 따라 호불호가 갈릴 수 있음</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>감기약 느낌의 향미 — 비타500과 감기약이 섞인 듯한 맛이 느껴짐</t>
-        </is>
-      </c>
+          <t>다소 느린 배송 — 다른 판매처 대비 배송 완료까지 시간이 약간 느린 편임</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>강한 생강 향미 호불호 — 생강 특유의 알싸하고 매운맛으로 인해 사람에 따라 거부감이 있을 수 있음</t>
-        </is>
-      </c>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4736,24 +4720,24 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
-        </is>
-      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>43,900원</t>
@@ -4761,7 +4745,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4935,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4959,12 +4943,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4974,28 +4958,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>834</v>
+        <v>2753</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 소포장 제품이라 가격 부담 없이 가성비 좋게 구매 가능함</t>
+          <t>배변 활동 원활 — 섭취 후 화장실을 잘 가게 되어 변비 해소에 효과적임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>비타민 복합 성분 구성 — 오메가3와 비타민 ADE가 함께 들어있어 간편하게 챙겨 먹기 좋음</t>
+          <t>뛰어난 가성비 — 합리적인 가격에 구매하여 다이어트 보조용으로 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5006,7 +4990,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5014,7 +4998,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5029,28 +5013,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/8husYxWOSsou1qKUi5IE613602128_00_018husYxWOSsou1qKUi5IE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1084</v>
+        <v>1583</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>저렴하고 높은 가성비 — 부담 없는 가격에 한 달 분량을 구매할 수 있어 만족스러움</t>
+          <t>아이들도 좋아하는 맛 — 맛과 향이 좋아 어린아이들도 거부감 없이 스스로 챙겨 먹음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>아이들이 잘 먹는 젤리 — 정제 알약보다 먹기 편하고 맛이 좋아 아이들도 잘 먹음</t>
+          <t>부담 없는 가성비 — 저렴한 가격대에 재구매하기 부담 없는 가성비 좋은 약국 아이템임</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -5061,7 +5045,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5069,47 +5053,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678607&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260825/1a3CLvRrBJMActwA3NW5601678607_00_021a3CLvRrBJMActwA3NW5.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1357</v>
+        <v>53</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 구미 — 달달하고 쫄깃하여 챙겨 먹기 편하고 맛이 우수함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>합리적인 가격 — 가격이 저렴하여 부담 없이 꾸준히 구매하기 좋음</t>
-        </is>
-      </c>
+          <t>맛있는 사과맛 제형 — 사과맛 과자처럼 달콤하고 맛있어서 철분제를 거부감 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>단단한 제형 및 3정 섭취 — 생각보다 식감이 단단하여 어르신이 씹기 힘들 수 있고 하루에 3정씩 복용해야 함</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5124,12 +5108,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5139,43 +5123,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>895</v>
+        <v>3483</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격이 매우 저렴하여 부담 없이 구매하기 좋음</t>
+          <t>소화 및 속 편안함 — 과식했거나 소화가 안 될 때 먹으면 속이 편안해지도록 도와줌</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>과식 후 체중 관리 — 많이 먹거나 칼로리가 걱정될 때 먹으면 마음이 편안해짐</t>
+          <t>우수한 휴대성 — 포장 크기가 작아 여행이나 외출 시 챙겨 다니기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>붓기 개선 효과 미미 — 복용 후에도 붓기 완화 등 체감되는 효과가 느껴지지 않음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5183,12 +5163,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5198,39 +5178,43 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1049</v>
+        <v>1344</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>착한 가격과 가성비 — 다이소에서 저렴하고 부담 없는 가격에 구매할 수 있음</t>
+          <t>붓기 완화 및 갈증 해소 — 외식이나 짠 음식을 먹은 후 마시면 붓기가 덜하고 갈증이 잘 해소됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>만족스러운 효과 — 제품 효능이 느껴지고 전반적인 사용 만족도가 높음</t>
+          <t>물 음용량 증가 — 맛이 좋아 물에 타서 마시면 평소보다 물을 더 많이 마시게 됨</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>잦은 상품 품절 — 인기가 많아 다이소몰에서 자주 품절되어 구하기 어려울 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5238,12 +5222,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5253,43 +5237,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>87</v>
+        <v>1611</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>간편한 기력 보충 — 지치고 힘들 때 하루 한 알씩 간편하게 먹기 좋음</t>
+          <t>뛰어난 요리 활용성 — 탄산수, 올리브오일, 각종 요리 등에 다채롭게 타서 활용하기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>저렴한 가격 — 부담 없는 가격으로 홍삼 제품을 구매할 수 있음</t>
+          <t>깔끔한 뒷맛 — 마시고 난 뒤의 뒷맛이 깔끔하여 매일 구비해두고 먹기 좋음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>쓸고 거북한 맛 — 환 특유의 쓰고 이상한 맛 때문에 섭취 후 뱉을 만큼 삼키기 힘듦</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5297,12 +5277,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5312,28 +5292,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/CJUce0AJqtqHn7R3ZFm1600000142_00_00CJUce0AJqtqHn7R3ZFm1.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>612</v>
+        <v>708</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>씹어 먹기 편한 츄어블 — 알약을 잘 못 삼키는 아이들이나 부모님도 쉽게 씹어 드실 수 있음</t>
+          <t>편리한 스쿱 섭취 — 스쿱으로 간편하게 떠먹을 수 있어 운동 전후로 사용하기 편리함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>맛있어서 매일 복용 — 맛이 좋아서 아이들이 거부감 없이 매일 챙겨 먹기 좋음</t>
+          <t>만족스러운 가성비 — 가격 대비 구성과 용량이 좋아 부담 없이 자주 구매하기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5352,54 +5332,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/G3OpB4vFrKk7H6gBBjO3601618634_00_00G3OpB4vFrKk7H6gBBjO3.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1341</v>
+        <v>809</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>맛있는 자몽 맛과 수분 섭취 — 달콤한 자몽 맛이라 물을 더 자주, 많이 마시게 됨</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>갈증 해소 및 붓기 관리 — 짠 음식 섭취 후 마시면 갈증이 해소되고 붓기 완화에 도움 됨</t>
-        </is>
-      </c>
+          <t>빠른 흡수 및 피로 회복 — 체내 흡수가 빨라 피로감이 느껴질 때 신속하게 에너지를 채워주는 느낌임</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>미세한 약맛 감돌음 — 복숭아 맛 뒤에 약간의 약 특유의 맛이 살짝 남을 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5407,12 +5387,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5422,28 +5402,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1611</v>
+        <v>1100</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>다양한 활용도 — 요리나 탄산수, 올리브오일 등에 타서 다양하게 활용하기 좋음</t>
+          <t>활력 보충 효과 — 섭취 시 몸에 활력이 느껴지고 기력 보충에 도움을 줌</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>깔끔한 뒷맛 — 마신 후 뒷맛이 깔끔하여 안 떨어지게 구비해 두기 좋음</t>
+          <t>충실한 가성비 — 저렴한 가격에 홍삼 본연의 기능에 충실하여 가성비가 높음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5454,7 +5434,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5462,12 +5442,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
+          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5477,28 +5457,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994852703&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910777&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260615/tjVLFd8X16oPgAvdvPpK994852703_00_00tjVLFd8X16oPgAvdvPpK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251229/5qFLremik89lsUa72Yqy610910777_00_005qFLremik89lsUa72Yqy.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>815</v>
+        <v>1173</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>새콤달콤한 사과 젤리 맛 — 살짝 시큼하면서도 달콤한 사과 맛이라 간식 대용으로 먹기 좋음</t>
+          <t>저렴한 혜자 가격 — 기본 비타민 D를 매우 저렴하고 가성비 있게 구매할 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 다이소에서 저렴한 가격으로 부담 없이 구매 가능함</t>
+          <t>작고 귀여운 알약 — 캡슐 크기가 귀엽고 작아서 목넘김 시 부담이 없음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5617,17 +5597,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5637,32 +5617,32 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>홍삼/인삼</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5654,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5684,42 +5664,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -5731,52 +5711,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>[혈액 생성] 동화약품 배러크런치 철분 사과맛 30정 10일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
+          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5767,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5796,13 +5776,13 @@
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
@@ -5814,7 +5794,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -5824,34 +5804,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>834</v>
+        <v>2753</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1084</v>
+        <v>1583</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1357</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>895</v>
+        <v>3483</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1049</v>
+        <v>1344</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>87</v>
+        <v>1611</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>612</v>
+        <v>708</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1341</v>
+        <v>809</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1611</v>
+        <v>1100</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>815</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5862,62 +5842,60 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 소포장 제품이라 가격 부담 없이 가성비 좋게 구매 가능함
-비타민 복합 성분 구성 — 오메가3와 비타민 ADE가 함께 들어있어 간편하게 챙겨 먹기 좋음</t>
+          <t>배변 활동 원활 — 섭취 후 화장실을 잘 가게 되어 변비 해소에 효과적임
+뛰어난 가성비 — 합리적인 가격에 구매하여 다이어트 보조용으로 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>저렴하고 높은 가성비 — 부담 없는 가격에 한 달 분량을 구매할 수 있어 만족스러움
-아이들이 잘 먹는 젤리 — 정제 알약보다 먹기 편하고 맛이 좋아 아이들도 잘 먹음</t>
+          <t>아이들도 좋아하는 맛 — 맛과 향이 좋아 어린아이들도 거부감 없이 스스로 챙겨 먹음
+부담 없는 가성비 — 저렴한 가격대에 재구매하기 부담 없는 가성비 좋은 약국 아이템임</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 구미 — 달달하고 쫄깃하여 챙겨 먹기 편하고 맛이 우수함
-합리적인 가격 — 가격이 저렴하여 부담 없이 꾸준히 구매하기 좋음</t>
+          <t>맛있는 사과맛 제형 — 사과맛 과자처럼 달콤하고 맛있어서 철분제를 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격이 매우 저렴하여 부담 없이 구매하기 좋음
-과식 후 체중 관리 — 많이 먹거나 칼로리가 걱정될 때 먹으면 마음이 편안해짐</t>
+          <t>소화 및 속 편안함 — 과식했거나 소화가 안 될 때 먹으면 속이 편안해지도록 도와줌
+우수한 휴대성 — 포장 크기가 작아 여행이나 외출 시 챙겨 다니기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격과 가성비 — 다이소에서 저렴하고 부담 없는 가격에 구매할 수 있음
-만족스러운 효과 — 제품 효능이 느껴지고 전반적인 사용 만족도가 높음</t>
+          <t>붓기 완화 및 갈증 해소 — 외식이나 짠 음식을 먹은 후 마시면 붓기가 덜하고 갈증이 잘 해소됨
+물 음용량 증가 — 맛이 좋아 물에 타서 마시면 평소보다 물을 더 많이 마시게 됨</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>간편한 기력 보충 — 지치고 힘들 때 하루 한 알씩 간편하게 먹기 좋음
-저렴한 가격 — 부담 없는 가격으로 홍삼 제품을 구매할 수 있음</t>
+          <t>뛰어난 요리 활용성 — 탄산수, 올리브오일, 각종 요리 등에 다채롭게 타서 활용하기 좋음
+깔끔한 뒷맛 — 마시고 난 뒤의 뒷맛이 깔끔하여 매일 구비해두고 먹기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>씹어 먹기 편한 츄어블 — 알약을 잘 못 삼키는 아이들이나 부모님도 쉽게 씹어 드실 수 있음
-맛있어서 매일 복용 — 맛이 좋아서 아이들이 거부감 없이 매일 챙겨 먹기 좋음</t>
+          <t>편리한 스쿱 섭취 — 스쿱으로 간편하게 떠먹을 수 있어 운동 전후로 사용하기 편리함
+만족스러운 가성비 — 가격 대비 구성과 용량이 좋아 부담 없이 자주 구매하기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 자몽 맛과 수분 섭취 — 달콤한 자몽 맛이라 물을 더 자주, 많이 마시게 됨
-갈증 해소 및 붓기 관리 — 짠 음식 섭취 후 마시면 갈증이 해소되고 붓기 완화에 도움 됨</t>
+          <t>빠른 흡수 및 피로 회복 — 체내 흡수가 빨라 피로감이 느껴질 때 신속하게 에너지를 채워주는 느낌임</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>다양한 활용도 — 요리나 탄산수, 올리브오일 등에 타서 다양하게 활용하기 좋음
-깔끔한 뒷맛 — 마신 후 뒷맛이 깔끔하여 안 떨어지게 구비해 두기 좋음</t>
+          <t>활력 보충 효과 — 섭취 시 몸에 활력이 느껴지고 기력 보충에 도움을 줌
+충실한 가성비 — 저렴한 가격에 홍삼 본연의 기능에 충실하여 가성비가 높음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>새콤달콤한 사과 젤리 맛 — 살짝 시큼하면서도 달콤한 사과 맛이라 간식 대용으로 먹기 좋음
-저렴한 가성비 — 다이소에서 저렴한 가격으로 부담 없이 구매 가능함</t>
+          <t>저렴한 혜자 가격 — 기본 비타민 D를 매우 저렴하고 가성비 있게 구매할 수 있음
+작고 귀여운 알약 — 캡슐 크기가 귀엽고 작아서 목넘김 시 부담이 없음</t>
         </is>
       </c>
     </row>
@@ -5929,20 +5907,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>붓기 개선 효과 미미 — 복용 후에도 붓기 완화 등 체감되는 효과가 느껴지지 않음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>쓸고 거북한 맛 — 환 특유의 쓰고 이상한 맛 때문에 섭취 후 뱉을 만큼 삼키기 힘듦</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>단단한 제형 및 3정 섭취 — 생각보다 식감이 단단하여 어르신이 씹기 힘들 수 있고 하루에 3정씩 복용해야 함</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>잦은 상품 품절 — 인기가 많아 다이소몰에서 자주 품절되어 구하기 어려울 수 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>미세한 약맛 감돌음 — 복숭아 맛 뒤에 약간의 약 특유의 맛이 살짝 남을 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
@@ -5964,32 +5946,32 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6178,7 +6160,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6186,27 +6168,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>미에로화이바</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19,800원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6221,7 +6203,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6229,45 +6211,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17,100원</t>
+          <t>19,800원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>2165</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 콜라보 — 마이멜로디, 키티 등 캐릭터 패키지와 굿즈가 매우 귀여움</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>배변 활동 및 체지방 관리 — 만성 변비 완화 및 아랫배 가벼워짐에 도움을 줌</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -6276,7 +6250,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6284,40 +6258,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1030</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>탄수화물 커팅과 안색 개선 — 탄수화물 분해 효소와 안색 및 간 건강에 도움 되는 글루타치온을 함께 챙김</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -6327,7 +6293,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6335,45 +6301,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,100원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>25493</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>목넘김이 편한 아주 작은 캡슐 — 캡슐 크기가 매우 작고 가벼워 목넘김 시 부담이 없음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 관리할 수 있어 지속적인 복용에 적합함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6382,7 +6336,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6390,58 +6344,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>9,500원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>26881</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>복부 관리 및 붓기 완화 — 과식 후 섭취 시 뱃살과 더부룩함이 정리되고 가벼워짐</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>귀여운 콜라보 패키지 — 헬로키티 디자인 패키지가 예뻐서 챙겨 먹는 재미가 있음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 알약 크기가 약간 커서 삼키는 데 부담이 있을 수 있음</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6449,27 +6387,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>아임비타</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -6515,22 +6453,10 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15582</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>편안한 수면 유도 — 자기 전에 챙겨 먹으면 뒤척임 없이 푹 잠드는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>맛있고 편한 구미 제형 — 물 없이 간편하게 씹어 먹을 수 있는 맛있는 젤리 형태임</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -6539,7 +6465,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6547,54 +6473,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,500원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>5137</v>
+        <v>26883</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 과일 맛 — 레몬라임, 복숭아 맛 등으로 간식처럼 맛있게 먹을 수 있음</t>
+          <t>원활한 배변 및 체지방 관리 — 화장실을 잘 가도록 도와주고 과식 후 뱃살 및 체지방 관리에 유용함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>물 없이 간편한 섭취 — 언제 어디서나 물 없이 간편하게 씹어 먹기 용이함</t>
+          <t>아침 붓기 완화 — 공복에 섭취 시 아침의 몸 무거움과 붓기를 줄여주는 느낌을 받음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>다소 큰 정제 크기 — 알약 타입의 경우 정제 크기가 약간 커서 삼키기 불편할 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6602,58 +6532,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>콜레올로지 버닝올로지 디데이 3.8g*5포 (5일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16,500원</t>
+          <t>19,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000170108&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017010823ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6511</v>
+        <v>16998</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>단기 체중 및 붓기 관리 — 과식 후 급하게 체중 및 붓기를 관리할 때 유용함</t>
+          <t>얼굴 라인 및 붓기 제거 — 야식을 먹었거나 중요한 촬영 전에 복용하면 얼굴 붓기 제거에 도움 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>휴대하기 편한 개별 포장 — 개별 포장으로 가방에 챙겨 다니며 먹기 편함</t>
+          <t>삼키기 쉬운 미니환 — 작은 미니환 제형이라 목넘김이 어렵지 않고 물과 함께 섭취하기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 5일분 구성 대비 가격이 다소 비싸게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6661,43 +6587,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2/3박스 (4개월/6개월분) +증정: 혈당케어프로 10일분</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63,800원</t>
+          <t>24,700원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000200764&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/B00000020076428ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>106</v>
+        <v>9496</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>상쾌한 츄어블 제형 — 사과나 자일리톨 맛으로 양치 후 간편히 씹어서 섭취 가능함</t>
+          <t>라인 및 붓기 관리 효과 — 맵단짠 음식이나 야식 섭취 후 부종을 줄이고 바디 라인을 관리해 줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>장 및 여성 건강 케어 — 꾸준히 섭취 시 장 건강과 여성 질 건강 관리에 도움을 줌</t>
+          <t>상큼한 포도맛 액상 — 물 없이 쭈욱 마실 수 있는 스틱 포 형태라 휴대가 간편하고 포도맛이라 맛있음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -6816,52 +6742,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6873,52 +6799,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>미에로화이바</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>아임비타</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>판도라</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
         </is>
       </c>
     </row>
@@ -6930,52 +6856,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 버닝올로지 디데이 3.8g*5포 (5일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2/3박스 (4개월/6개월분) +증정: 혈당케어프로 10일분</t>
         </is>
       </c>
     </row>
@@ -6987,29 +6913,21 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7020,29 +6938,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="n">
-        <v>2165</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1030</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>25493</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>26881</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>15582</v>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>5137</v>
+        <v>26883</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6511</v>
+        <v>16998</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>106</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -7052,52 +6962,28 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 콜라보 — 마이멜로디, 키티 등 캐릭터 패키지와 굿즈가 매우 귀여움
-배변 활동 및 체지방 관리 — 만성 변비 완화 및 아랫배 가벼워짐에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>탄수화물 커팅과 안색 개선 — 탄수화물 분해 효소와 안색 및 간 건강에 도움 되는 글루타치온을 함께 챙김</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>목넘김이 편한 아주 작은 캡슐 — 캡슐 크기가 매우 작고 가벼워 목넘김 시 부담이 없음
-질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 관리할 수 있어 지속적인 복용에 적합함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>복부 관리 및 붓기 완화 — 과식 후 섭취 시 뱃살과 더부룩함이 정리되고 가벼워짐
-귀여운 콜라보 패키지 — 헬로키티 디자인 패키지가 예뻐서 챙겨 먹는 재미가 있음</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>편안한 수면 유도 — 자기 전에 챙겨 먹으면 뒤척임 없이 푹 잠드는 데 도움을 줌
-맛있고 편한 구미 제형 — 물 없이 간편하게 씹어 먹을 수 있는 맛있는 젤리 형태임</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 과일 맛 — 레몬라임, 복숭아 맛 등으로 간식처럼 맛있게 먹을 수 있음
-물 없이 간편한 섭취 — 언제 어디서나 물 없이 간편하게 씹어 먹기 용이함</t>
+          <t>원활한 배변 및 체지방 관리 — 화장실을 잘 가도록 도와주고 과식 후 뱃살 및 체지방 관리에 유용함
+아침 붓기 완화 — 공복에 섭취 시 아침의 몸 무거움과 붓기를 줄여주는 느낌을 받음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>단기 체중 및 붓기 관리 — 과식 후 급하게 체중 및 붓기를 관리할 때 유용함
-휴대하기 편한 개별 포장 — 개별 포장으로 가방에 챙겨 다니며 먹기 편함</t>
+          <t>얼굴 라인 및 붓기 제거 — 야식을 먹었거나 중요한 촬영 전에 복용하면 얼굴 붓기 제거에 도움 됨
+삼키기 쉬운 미니환 — 작은 미니환 제형이라 목넘김이 어렵지 않고 물과 함께 섭취하기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>상쾌한 츄어블 제형 — 사과나 자일리톨 맛으로 양치 후 간편히 씹어서 섭취 가능함
-장 및 여성 건강 케어 — 꾸준히 섭취 시 장 건강과 여성 질 건강 관리에 도움을 줌</t>
+          <t>라인 및 붓기 관리 효과 — 맵단짠 음식이나 야식 섭취 후 부종을 줄이고 바디 라인을 관리해 줌
+상큼한 포도맛 액상 — 물 없이 쭈욱 마실 수 있는 스틱 포 형태라 휴대가 간편하고 포도맛이라 맛있음</t>
         </is>
       </c>
     </row>
@@ -7111,19 +6997,15 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 알약 크기가 약간 커서 삼키는 데 부담이 있을 수 있음</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 5일분 구성 대비 가격이 다소 비싸게 느껴짐</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 정제 크기 — 알약 타입의 경우 정제 크기가 약간 커서 삼키기 불편할 수 있음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7134,52 +7016,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>19,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>17,100원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>19,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>24,700원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>9,500원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>16,500원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>63,800원</t>
         </is>
       </c>
     </row>
@@ -7309,16 +7191,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -7327,7 +7209,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7337,19 +7219,19 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7359,13 +7241,13 @@
         <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7393,7 +7275,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7403,10 +7285,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7415,7 +7297,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7428,32 +7310,32 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
